--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Futbol\Temporada 2027\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCBC930A-1939-41F9-96B4-B0CC9B00EFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7372390-8D0C-4E63-BFE2-B4FE92DAC017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F7C7B841-2D69-4C43-9B67-F8FAFE3EB694}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Name</t>
   </si>
@@ -34,39 +34,6 @@
     <t>Photo</t>
   </si>
   <si>
-    <t>2.jpg</t>
-  </si>
-  <si>
-    <t>3.jpg</t>
-  </si>
-  <si>
-    <t>5.jpg</t>
-  </si>
-  <si>
-    <t>6.jpg</t>
-  </si>
-  <si>
-    <t>7.jpg</t>
-  </si>
-  <si>
-    <t>9.jpg</t>
-  </si>
-  <si>
-    <t>10.jpg</t>
-  </si>
-  <si>
-    <t>15.jpg</t>
-  </si>
-  <si>
-    <t>19.jpg</t>
-  </si>
-  <si>
-    <t>20.jpg</t>
-  </si>
-  <si>
-    <t>34.jpg</t>
-  </si>
-  <si>
     <t>36.jpg</t>
   </si>
   <si>
@@ -76,18 +43,12 @@
     <t>52.jpg</t>
   </si>
   <si>
-    <t>55.jpg</t>
-  </si>
-  <si>
     <t>59.jpg</t>
   </si>
   <si>
     <t>60.jpg</t>
   </si>
   <si>
-    <t>66.jpg</t>
-  </si>
-  <si>
     <t>71.jpg</t>
   </si>
   <si>
@@ -197,6 +158,60 @@
   </si>
   <si>
     <t>Enzo</t>
+  </si>
+  <si>
+    <t>2.png</t>
+  </si>
+  <si>
+    <t>3.png</t>
+  </si>
+  <si>
+    <t>5.png</t>
+  </si>
+  <si>
+    <t>6.png</t>
+  </si>
+  <si>
+    <t>7.png</t>
+  </si>
+  <si>
+    <t>9.png</t>
+  </si>
+  <si>
+    <t>10.png</t>
+  </si>
+  <si>
+    <t>15.png</t>
+  </si>
+  <si>
+    <t>19.png</t>
+  </si>
+  <si>
+    <t>20.png</t>
+  </si>
+  <si>
+    <t>66.png</t>
+  </si>
+  <si>
+    <t>Elen</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>Monkey</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>55.png</t>
+  </si>
+  <si>
+    <t>34.png</t>
   </si>
 </sst>
 </file>
@@ -1059,292 +1074,307 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B9">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B12">
         <v>34</v>
       </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B14">
         <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>55</v>
       </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>66</v>
       </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>98</v>
       </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B26">
         <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
